--- a/AAII_Financials/Yearly/BMNM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BMNM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>BMNM</t>
   </si>
@@ -699,7 +699,7 @@
         <v>44196</v>
       </c>
       <c r="J7" s="2">
-        <v>43830</v>
+        <v>43465</v>
       </c>
       <c r="K7" s="2">
         <v>43465</v>
@@ -732,25 +732,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>17100</v>
+        <v>23900</v>
       </c>
       <c r="E8" s="3">
-        <v>13100</v>
+        <v>20600</v>
       </c>
       <c r="F8" s="3">
-        <v>10600</v>
+        <v>16100</v>
       </c>
       <c r="G8" s="3">
-        <v>1900</v>
+        <v>4000</v>
       </c>
       <c r="H8" s="3">
-        <v>8200</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>8</v>
+        <v>9300</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2000</v>
       </c>
       <c r="J8" s="3">
-        <v>10100</v>
+        <v>6300</v>
       </c>
       <c r="K8" s="3">
         <v>800</v>
@@ -782,26 +782,26 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
+      <c r="D9" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>9000</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>8</v>
+      <c r="G9" s="3">
+        <v>7900</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>8</v>
+      <c r="I9" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J9" s="3">
+        <v>4000</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>8</v>
@@ -834,25 +834,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>17100</v>
+        <v>13900</v>
       </c>
       <c r="E10" s="3">
-        <v>13100</v>
+        <v>11700</v>
       </c>
       <c r="F10" s="3">
-        <v>10600</v>
+        <v>16100</v>
       </c>
       <c r="G10" s="3">
-        <v>1900</v>
+        <v>-3900</v>
       </c>
       <c r="H10" s="3">
-        <v>8200</v>
+        <v>9300</v>
       </c>
       <c r="I10" s="3">
-        <v>-200</v>
+        <v>-2200</v>
       </c>
       <c r="J10" s="3">
-        <v>10100</v>
+        <v>2300</v>
       </c>
       <c r="K10" s="3">
         <v>800</v>
@@ -1025,8 +1025,8 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>700</v>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1179,25 +1179,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4500</v>
+        <v>11300</v>
       </c>
       <c r="E18" s="3">
-        <v>1800</v>
+        <v>9400</v>
       </c>
       <c r="F18" s="3">
-        <v>100</v>
+        <v>5600</v>
       </c>
       <c r="G18" s="3">
-        <v>-8000</v>
+        <v>-5800</v>
       </c>
       <c r="H18" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J18" s="3">
         <v>-100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="J18" s="3">
-        <v>3700</v>
       </c>
       <c r="K18" s="3">
         <v>-5700</v>
@@ -1302,25 +1302,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4600</v>
+        <v>11400</v>
       </c>
       <c r="E21" s="3">
-        <v>1900</v>
+        <v>9400</v>
       </c>
       <c r="F21" s="3">
-        <v>200</v>
+        <v>5600</v>
       </c>
       <c r="G21" s="3">
-        <v>-7900</v>
+        <v>-5800</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I21" s="3">
-        <v>-6800</v>
+        <v>-4600</v>
       </c>
       <c r="J21" s="3">
-        <v>3800</v>
+        <v>-100</v>
       </c>
       <c r="K21" s="3">
         <v>-5600</v>
@@ -1352,26 +1352,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="G22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J22" s="3">
+        <v>5500</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>8</v>
@@ -1422,7 +1422,7 @@
         <v>-6900</v>
       </c>
       <c r="J23" s="3">
-        <v>3000</v>
+        <v>-5700</v>
       </c>
       <c r="K23" s="3">
         <v>-5700</v>
@@ -1473,7 +1473,7 @@
         <v>-1400</v>
       </c>
       <c r="J24" s="3">
-        <v>-10300</v>
+        <v>21100</v>
       </c>
       <c r="K24" s="3">
         <v>21100</v>
@@ -1575,7 +1575,7 @@
         <v>-5500</v>
       </c>
       <c r="J26" s="3">
-        <v>13300</v>
+        <v>-26800</v>
       </c>
       <c r="K26" s="3">
         <v>-26800</v>
@@ -1626,7 +1626,7 @@
         <v>-5500</v>
       </c>
       <c r="J27" s="3">
-        <v>13300</v>
+        <v>-26800</v>
       </c>
       <c r="K27" s="3">
         <v>-26800</v>
@@ -1932,7 +1932,7 @@
         <v>-5500</v>
       </c>
       <c r="J33" s="3">
-        <v>13300</v>
+        <v>-26800</v>
       </c>
       <c r="K33" s="3">
         <v>-26800</v>
@@ -2034,7 +2034,7 @@
         <v>-5500</v>
       </c>
       <c r="J35" s="3">
-        <v>13300</v>
+        <v>-26800</v>
       </c>
       <c r="K35" s="3">
         <v>-26800</v>
@@ -2090,7 +2090,7 @@
         <v>44196</v>
       </c>
       <c r="J38" s="2">
-        <v>43830</v>
+        <v>43465</v>
       </c>
       <c r="K38" s="2">
         <v>43465</v>
@@ -2183,7 +2183,7 @@
         <v>7600</v>
       </c>
       <c r="J41" s="3">
-        <v>8100</v>
+        <v>4900</v>
       </c>
       <c r="K41" s="3">
         <v>4900</v>
@@ -2285,7 +2285,7 @@
         <v>800</v>
       </c>
       <c r="J43" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="K43" s="3">
         <v>1700</v>
@@ -2368,26 +2368,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>200</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
-        <v>300</v>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H45" s="3">
-        <v>500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>500</v>
+        <v>200</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J45" s="3">
-        <v>2400</v>
+        <v>1600</v>
       </c>
       <c r="K45" s="3">
         <v>1900</v>
@@ -2435,10 +2435,10 @@
         <v>11600</v>
       </c>
       <c r="I46" s="3">
-        <v>12200</v>
+        <v>12000</v>
       </c>
       <c r="J46" s="3">
-        <v>16400</v>
+        <v>9800</v>
       </c>
       <c r="K46" s="3">
         <v>9800</v>
@@ -2489,7 +2489,7 @@
         <v>14400</v>
       </c>
       <c r="J47" s="3">
-        <v>9700</v>
+        <v>10600</v>
       </c>
       <c r="K47" s="3">
         <v>10600</v>
@@ -2540,7 +2540,7 @@
         <v>2100</v>
       </c>
       <c r="J48" s="3">
-        <v>2200</v>
+        <v>3300</v>
       </c>
       <c r="K48" s="3">
         <v>3300</v>
@@ -2741,10 +2741,10 @@
         <v>61000</v>
       </c>
       <c r="I52" s="3">
-        <v>65300</v>
+        <v>65500</v>
       </c>
       <c r="J52" s="3">
-        <v>217900</v>
+        <v>212500</v>
       </c>
       <c r="K52" s="3">
         <v>212500</v>
@@ -2846,7 +2846,7 @@
         <v>128700</v>
       </c>
       <c r="J54" s="3">
-        <v>279500</v>
+        <v>259400</v>
       </c>
       <c r="K54" s="3">
         <v>259400</v>
@@ -2920,20 +2920,20 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>8</v>
+      <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>100</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>8</v>
+      <c r="G57" s="3">
+        <v>100</v>
+      </c>
+      <c r="H57" s="3">
+        <v>0</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>8</v>
@@ -2990,7 +2990,7 @@
         <v>65100</v>
       </c>
       <c r="J58" s="3">
-        <v>210000</v>
+        <v>200400</v>
       </c>
       <c r="K58" s="3">
         <v>201300</v>
@@ -3040,8 +3040,8 @@
       <c r="I59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
+      <c r="J59" s="3">
+        <v>900</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>8</v>
@@ -3074,25 +3074,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>85600</v>
+        <v>89700</v>
       </c>
       <c r="E60" s="3">
-        <v>117700</v>
+        <v>120700</v>
       </c>
       <c r="F60" s="3">
         <v>87200</v>
       </c>
       <c r="G60" s="3">
-        <v>44000</v>
+        <v>46800</v>
       </c>
       <c r="H60" s="3">
-        <v>58900</v>
+        <v>61600</v>
       </c>
       <c r="I60" s="3">
         <v>65200</v>
       </c>
       <c r="J60" s="3">
-        <v>210700</v>
+        <v>202000</v>
       </c>
       <c r="K60" s="3">
         <v>202000</v>
@@ -3143,7 +3143,7 @@
         <v>27600</v>
       </c>
       <c r="J61" s="3">
-        <v>27500</v>
+        <v>26800</v>
       </c>
       <c r="K61" s="3">
         <v>26800</v>
@@ -3175,26 +3175,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>4100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3000</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F62" s="3">
         <v>2900</v>
       </c>
-      <c r="G62" s="3">
-        <v>2800</v>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H62" s="3">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
         <v>1400</v>
       </c>
       <c r="J62" s="3">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="K62" s="3">
         <v>1600</v>
@@ -3398,7 +3398,7 @@
         <v>94200</v>
       </c>
       <c r="J66" s="3">
-        <v>239500</v>
+        <v>230400</v>
       </c>
       <c r="K66" s="3">
         <v>230400</v>
@@ -3674,7 +3674,7 @@
         <v>-298200</v>
       </c>
       <c r="J72" s="3">
-        <v>-292700</v>
+        <v>-306000</v>
       </c>
       <c r="K72" s="3">
         <v>-306000</v>
@@ -3878,7 +3878,7 @@
         <v>34500</v>
       </c>
       <c r="J76" s="3">
-        <v>40000</v>
+        <v>29000</v>
       </c>
       <c r="K76" s="3">
         <v>29000</v>
@@ -3985,7 +3985,7 @@
         <v>44196</v>
       </c>
       <c r="J80" s="2">
-        <v>43830</v>
+        <v>43465</v>
       </c>
       <c r="K80" s="2">
         <v>43465</v>
@@ -4036,7 +4036,7 @@
         <v>-5500</v>
       </c>
       <c r="J81" s="3">
-        <v>13300</v>
+        <v>-26800</v>
       </c>
       <c r="K81" s="3">
         <v>-26800</v>
@@ -4414,7 +4414,7 @@
         <v>1300</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="K89" s="3">
         <v>6400</v>
@@ -4485,8 +4485,8 @@
       <c r="I91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
+      <c r="J91" s="3">
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4639,7 +4639,7 @@
         <v>142000</v>
       </c>
       <c r="J94" s="3">
-        <v>-1800</v>
+        <v>-9100</v>
       </c>
       <c r="K94" s="3">
         <v>-9100</v>
@@ -4915,7 +4915,7 @@
         <v>-144800</v>
       </c>
       <c r="J100" s="3">
-        <v>8000</v>
+        <v>200</v>
       </c>
       <c r="K100" s="3">
         <v>200</v>
@@ -5017,7 +5017,7 @@
         <v>-1500</v>
       </c>
       <c r="J102" s="3">
-        <v>6100</v>
+        <v>-2500</v>
       </c>
       <c r="K102" s="3">
         <v>-2500</v>
